--- a/artfynd/A 21091-2022 artfynd.xlsx
+++ b/artfynd/A 21091-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21091-2022 artfynd.xlsx
+++ b/artfynd/A 21091-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6231985</v>
+        <v>279307</v>
       </c>
       <c r="B2" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224365</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallåsen / bäck 450 m S /, Frostviken, Jmt</t>
+          <t>Vallåns Natura 2000-område, vid Vallåns Vra strand, O om skjutvallen,, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453415.2003938289</v>
+        <v>453115</v>
       </c>
       <c r="R2" t="n">
-        <v>7179974.536019919</v>
+        <v>7179345</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +741,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observatör Bengt Petterson. Ca 450 m söder om Vallåsen, vid liten bäck öster om landsvägen, i skogsbryn mot vägen.</t>
+          <t>ca 350 m N om landsvägsbron,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,33 +765,37 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal granskog, bakslänt vägkant / skogsbryn</t>
+          <t>Alluvial aldominerad lövskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Alved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tobias Ekendahl</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2710362</v>
+        <v>579354</v>
       </c>
       <c r="B3" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>1549</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Sätertrumpetmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Tayloria splachnoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Schleich. ex Schwägr.) Hook.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453121.4092188583</v>
+        <v>453216</v>
       </c>
       <c r="R3" t="n">
-        <v>7179099.256500347</v>
+        <v>7179664</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,65 +874,79 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flack liten älvdal med fjällnära barrskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>flackt block med rikförna</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59823736</v>
+        <v>457218</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219880</v>
+        <v>1845</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svämskapania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Scapania glaucocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Taylor) Austin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vallåsen, ca 400 m m söder om, vid liten bäck öster om landsvägen, vid hygg, Jmt</t>
+          <t>Vallån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453465.7210177403</v>
+        <v>453129</v>
       </c>
       <c r="R4" t="n">
-        <v>7180088.256176047</v>
+        <v>7179423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,27 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal granskog, hyggeskant</t>
+          <t>2006-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,31 +989,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bred strömmande å</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granstubbe i åkanten</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59823737</v>
+        <v>60918576</v>
       </c>
       <c r="B5" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>2082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallåsen, ca 450 m m söder om, vid liten bäck öster om landsvägen, ca 75 m , Jmt</t>
+          <t>Vallåsen, ca 500 m m söder om, örtrik fuktsänka, periodisk bäck, öster om l, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453447.5731849832</v>
+        <v>453498</v>
       </c>
       <c r="R5" t="n">
-        <v>7180021.03299368</v>
+        <v>7179988</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,24 +1088,14 @@
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gammal granskog</t>
+          <t>Gammal lätt gallrad granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59823735</v>
+        <v>60918577</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1133,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>2082</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vallåsen, ca 500 m m söder om, örtrik fuktsänka och periodisk bäck öster om, Jmt</t>
+          <t>Vallåsen, ca 450 m m söder om, vid liten bäck öster om landsvägen, ca 75 m , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453497.9645502386</v>
+        <v>453448</v>
       </c>
       <c r="R6" t="n">
-        <v>7179987.785154482</v>
+        <v>7180021</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,24 +1190,14 @@
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal lätt gallrad granskog</t>
+          <t>Gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>60918576</v>
+        <v>1865872</v>
       </c>
       <c r="B7" t="n">
-        <v>97552</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,34 +1235,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2082</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallåsen, ca 500 m m söder om, örtrik fuktsänka, periodisk bäck, öster om l, Jmt</t>
+          <t>Vallåns Natura 2000-område, vid Vallåns Vra strand, O om skjutvallen,, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453497.9645502386</v>
+        <v>453115</v>
       </c>
       <c r="R7" t="n">
-        <v>7179987.785154482</v>
+        <v>7179345</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,27 +1290,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-08-24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal lätt gallrad granskog</t>
+          <t>ca 350 m N om landsvägsbron,</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,31 +1311,40 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Alluvial aldominerad lövskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Granpinne</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Tobias Ekendahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60918577</v>
+        <v>59823735</v>
       </c>
       <c r="B8" t="n">
-        <v>97552</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,34 +1352,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2082</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vallåsen, ca 450 m m söder om, vid liten bäck öster om landsvägen, ca 75 m , Jmt</t>
+          <t>Vallåsen, ca 500 m m söder om, örtrik fuktsänka och periodisk bäck öster om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>453447.5731849832</v>
+        <v>453498</v>
       </c>
       <c r="R8" t="n">
-        <v>7180021.03299368</v>
+        <v>7179988</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,24 +1409,14 @@
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2000-07-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammal granskog</t>
+          <t>Gammal lätt gallrad granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,6 +1440,414 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>59823736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vallåsen, ca 400 m m söder om, vid liten bäck öster om landsvägen, vid hygg, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>453466</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7180088</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal granskog, hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>59823737</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallåsen, ca 450 m m söder om, vid liten bäck öster om landsvägen, ca 75 m , Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>453448</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7180021</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2710362</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>453121</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7179099</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2011-07-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2011-07-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6231985</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97988</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224365</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Riplummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallåsen / bäck 450 m S /, Frostviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>453415</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7179975</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2000-06-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2000-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Observatör Bengt Petterson. Ca 450 m söder om Vallåsen, vid liten bäck öster om landsvägen, i skogsbryn mot vägen.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog, bakslänt vägkant / skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21091-2022 artfynd.xlsx
+++ b/artfynd/A 21091-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/279307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/579354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/457218</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60918576</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60918577</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1865872</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59823735</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59823736</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59823737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2710362</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,8 +1903,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6231985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>